--- a/Liquid+ Project/Sélection des startups/processus de sélection des startups BAPTISTE.xlsx
+++ b/Liquid+ Project/Sélection des startups/processus de sélection des startups BAPTISTE.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1734" uniqueCount="930">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1794" uniqueCount="962">
   <si>
     <t>Implantation</t>
   </si>
@@ -2556,7 +2556,7 @@
     <t>nom</t>
   </si>
   <si>
-    <t>Column 9</t>
+    <t>Mail</t>
   </si>
   <si>
     <t>stade</t>
@@ -2571,21 +2571,33 @@
     <t>trouvée sur ?</t>
   </si>
   <si>
-    <t>mail</t>
-  </si>
-  <si>
-    <t>linkedin</t>
+    <t>Linkedin perso</t>
+  </si>
+  <si>
+    <t>linkedin marque</t>
   </si>
   <si>
     <t>Ampe-RF</t>
   </si>
   <si>
+    <t>privacy@ampe-rf.com</t>
+  </si>
+  <si>
     <t>Dispositif médical / radiofréquence (nouvel adhérent Eurobiomed 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/victor-g-329ab512/</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
     <t>Care AI Solutions</t>
   </si>
   <si>
+    <t>hello@care.ai</t>
+  </si>
+  <si>
     <t>Intelligence artificielle appliquée à la santé (nouvel adhérent 2025)</t>
   </si>
   <si>
@@ -2607,12 +2619,23 @@
     <t>Services santé et autonomie (nouvel adhérent 2025)</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
     <t>Mothair</t>
   </si>
   <si>
+    <t xml:space="preserve">contact@mothair.fr
+contact@mothair.fr
+</t>
+  </si>
+  <si>
     <t>Santé respiratoire / dispositif (nouvel adhérent 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/damienvert/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/mothair</t>
   </si>
   <si>
@@ -2625,10 +2648,13 @@
     <t>Pylote</t>
   </si>
   <si>
+    <t>contact@pylote.com</t>
+  </si>
+  <si>
     <t>Matériaux biocides / antimicrobiens (nouvel adhérent 2025)</t>
   </si>
   <si>
-    <t>contact@pylote.com</t>
+    <t/>
   </si>
   <si>
     <t>https://www.linkedin.com/company/pylote</t>
@@ -2640,12 +2666,27 @@
     <t>Biotech (nouvel adhérent 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/lionelbrodard/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/soteriabio/people/</t>
+  </si>
+  <si>
     <t>Orius</t>
   </si>
   <si>
+    <t>contact@orius.co</t>
+  </si>
+  <si>
     <t>E-santé (nouvel adhérent Biorézo 2024)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/pierre-jay/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/orius-sas/</t>
+  </si>
+  <si>
     <t>ABIONYX Pharma</t>
   </si>
   <si>
@@ -2661,15 +2702,24 @@
     <t>Magic Genomix</t>
   </si>
   <si>
+    <t>contact@magic-genomix.com</t>
+  </si>
+  <si>
     <t>Génomique / diagnostic (nouvel adhérent 2024)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/frederic-nahon-magic-genomix/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/magic-genomix</t>
   </si>
   <si>
     <t>Nanoscale Metrix</t>
   </si>
   <si>
+    <t>sarazin@nanoscale-metrix.com</t>
+  </si>
+  <si>
     <t>Métrologie nano pour la santé (nouvel adhérent 2024)</t>
   </si>
   <si>
@@ -2682,12 +2732,23 @@
     <t>Biotech (nouvel adhérent 2024)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/adreogen/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Icovell</t>
   </si>
   <si>
+    <t xml:space="preserve">contact@icovell.frcontact@icovell.fr
+contact@icovell.fr
+</t>
+  </si>
+  <si>
     <t>E-santé (nouvel adhérent 2024)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/icovell/</t>
+  </si>
+  <si>
     <t>Pytheas Navigation</t>
   </si>
   <si>
@@ -2709,15 +2770,24 @@
     <t>Luna</t>
   </si>
   <si>
+    <t>question@luna-endo.fr</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/ines-ben-amor/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/lunaforhealth/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Dimicare</t>
   </si>
   <si>
+    <t>juan.garcia@dimicare-biotech.com</t>
+  </si>
+  <si>
     <t>Dispositif médical / e-santé (présentée à Nice 2025)</t>
   </si>
   <si>
-    <t>juan.garcia@dimicare-biotech.com</t>
-  </si>
-  <si>
     <t>https://www.linkedin.com/company/dimicare-biotech</t>
   </si>
   <si>
@@ -2727,6 +2797,9 @@
     <t>Robotique chirurgicale assistée par IA (présentée à Nice 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/jhprofile/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/caranx-medical</t>
   </si>
   <si>
@@ -2736,6 +2809,12 @@
     <t>Tech santé / data (présentée à Nice 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/dimopoulou/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/pearcode/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Phenocell</t>
   </si>
   <si>
@@ -2766,12 +2845,21 @@
     <t>Sécurisation de lablation de la fibrillation atriale (levée 8 M€ 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/bertrandthiery/</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/company/circle-safe/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>Eka Surgery</t>
   </si>
   <si>
     <t>Plateforme IA daide aux chirurgiens (en levée 2025)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/company/ekasurgery/?originalSubdomain=fr</t>
+  </si>
+  <si>
     <t>MedinCell</t>
   </si>
   <si>
@@ -2799,16 +2887,28 @@
     <t>REEV</t>
   </si>
   <si>
+    <t>hello@reev.care</t>
+  </si>
+  <si>
     <t>Dispositif médical - rééducation à la marche (levée 8,8 M€)</t>
   </si>
   <si>
+    <t>https://www.linkedin.com/in/amauryciurana/</t>
+  </si>
+  <si>
     <t>https://www.linkedin.com/company/reevcare</t>
   </si>
   <si>
     <t>BOYDSense</t>
   </si>
   <si>
+    <t>contact@boydsense.com</t>
+  </si>
+  <si>
     <t>Diagnostic non invasif par lhaleine (levée 7 M€)</t>
+  </si>
+  <si>
+    <t>https://www.linkedin.com/in/bendelhey/</t>
   </si>
   <si>
     <t>https://www.linkedin.com/company/boydsense</t>
@@ -2848,12 +2948,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
     <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="general"/>
     </xf>
   </cellXfs>
@@ -9688,10 +9791,12 @@
       <c r="B500" s="1" t="s">
         <v>851</v>
       </c>
-      <c r="C500" s="1"/>
+      <c r="C500" s="1" t="s">
+        <v>852</v>
+      </c>
       <c r="D500" s="1"/>
       <c r="E500" s="1" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="F500" s="1"/>
       <c r="G500" s="1"/>
@@ -9699,18 +9804,24 @@
       <c r="I500" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J500" s="1"/>
+      <c r="J500" s="1" t="s">
+        <v>854</v>
+      </c>
       <c r="K500" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="501" customHeight="1" ht="18.75">
-      <c r="A501" s="1"/>
+      <c r="A501" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B501" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="C501" s="1"/>
+        <v>856</v>
+      </c>
+      <c r="C501" s="1" t="s">
+        <v>857</v>
+      </c>
       <c r="D501" s="1"/>
       <c r="E501" s="1" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="F501" s="1"/>
       <c r="G501" s="1"/>
@@ -9722,14 +9833,16 @@
       <c r="K501" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="502" customHeight="1" ht="18.75">
-      <c r="A502" s="1"/>
+      <c r="A502" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B502" s="1" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="C502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="F502" s="1"/>
       <c r="G502" s="1"/>
@@ -9741,14 +9854,16 @@
       <c r="K502" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="503" customHeight="1" ht="18.75">
-      <c r="A503" s="1"/>
+      <c r="A503" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B503" s="1" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="C503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="F503" s="1"/>
       <c r="G503" s="1"/>
@@ -9760,14 +9875,16 @@
       <c r="K503" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="504" customHeight="1" ht="18.75">
-      <c r="A504" s="1"/>
+      <c r="A504" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B504" s="1" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="C504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="F504" s="1"/>
       <c r="G504" s="1"/>
@@ -9779,14 +9896,18 @@
       <c r="K504" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="505" customHeight="1" ht="18.75">
-      <c r="A505" s="1"/>
+      <c r="A505" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B505" s="1" t="s">
-        <v>861</v>
-      </c>
-      <c r="C505" s="1"/>
+        <v>866</v>
+      </c>
+      <c r="C505" s="1" t="s">
+        <v>867</v>
+      </c>
       <c r="D505" s="1"/>
       <c r="E505" s="1" t="s">
-        <v>862</v>
+        <v>868</v>
       </c>
       <c r="F505" s="1"/>
       <c r="G505" s="1"/>
@@ -9794,20 +9915,24 @@
       <c r="I505" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J505" s="1"/>
+      <c r="J505" s="1" t="s">
+        <v>869</v>
+      </c>
       <c r="K505" s="1" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="506" customHeight="1" ht="18.75">
-      <c r="A506" s="1"/>
+      <c r="A506" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B506" s="1" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="C506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="F506" s="1"/>
       <c r="G506" s="1"/>
@@ -9819,14 +9944,18 @@
       <c r="K506" s="1"/>
     </row>
     <row x14ac:dyDescent="0.25" r="507" customHeight="1" ht="18.75">
-      <c r="A507" s="1"/>
+      <c r="A507" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B507" s="1" t="s">
-        <v>866</v>
-      </c>
-      <c r="C507" s="1"/>
+        <v>873</v>
+      </c>
+      <c r="C507" s="1" t="s">
+        <v>874</v>
+      </c>
       <c r="D507" s="1"/>
       <c r="E507" s="1" t="s">
-        <v>867</v>
+        <v>875</v>
       </c>
       <c r="F507" s="1"/>
       <c r="G507" s="1"/>
@@ -9834,22 +9963,26 @@
       <c r="I507" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J507" s="1" t="s">
-        <v>868</v>
+      <c r="J507" s="3" t="s">
+        <v>876</v>
       </c>
       <c r="K507" s="1" t="s">
-        <v>869</v>
+        <v>877</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="508" customHeight="1" ht="18.75">
-      <c r="A508" s="1"/>
+      <c r="A508" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B508" s="1" t="s">
-        <v>870</v>
-      </c>
-      <c r="C508" s="1"/>
+        <v>878</v>
+      </c>
+      <c r="C508" s="3" t="s">
+        <v>876</v>
+      </c>
       <c r="D508" s="1"/>
       <c r="E508" s="1" t="s">
-        <v>871</v>
+        <v>879</v>
       </c>
       <c r="F508" s="1"/>
       <c r="G508" s="1"/>
@@ -9857,18 +9990,26 @@
       <c r="I508" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J508" s="1"/>
-      <c r="K508" s="1"/>
+      <c r="J508" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="K508" s="1" t="s">
+        <v>881</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="509" customHeight="1" ht="18.75">
-      <c r="A509" s="1"/>
+      <c r="A509" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B509" s="1" t="s">
-        <v>872</v>
-      </c>
-      <c r="C509" s="1"/>
+        <v>882</v>
+      </c>
+      <c r="C509" s="1" t="s">
+        <v>883</v>
+      </c>
       <c r="D509" s="1"/>
       <c r="E509" s="1" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="F509" s="1"/>
       <c r="G509" s="1"/>
@@ -9876,20 +10017,26 @@
       <c r="I509" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J509" s="1"/>
-      <c r="K509" s="1"/>
+      <c r="J509" s="1" t="s">
+        <v>885</v>
+      </c>
+      <c r="K509" s="1" t="s">
+        <v>886</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="510" customHeight="1" ht="18.75">
-      <c r="A510" s="1"/>
+      <c r="A510" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B510" s="1" t="s">
-        <v>874</v>
+        <v>887</v>
       </c>
       <c r="C510" s="1"/>
       <c r="D510" s="1" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="E510" s="1" t="s">
-        <v>876</v>
+        <v>889</v>
       </c>
       <c r="F510" s="1"/>
       <c r="G510" s="1"/>
@@ -9899,18 +10046,22 @@
       </c>
       <c r="J510" s="1"/>
       <c r="K510" s="1" t="s">
-        <v>877</v>
+        <v>890</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="511" customHeight="1" ht="18.75">
-      <c r="A511" s="1"/>
+      <c r="A511" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B511" s="1" t="s">
-        <v>878</v>
-      </c>
-      <c r="C511" s="1"/>
+        <v>891</v>
+      </c>
+      <c r="C511" s="1" t="s">
+        <v>892</v>
+      </c>
       <c r="D511" s="1"/>
       <c r="E511" s="1" t="s">
-        <v>879</v>
+        <v>893</v>
       </c>
       <c r="F511" s="1"/>
       <c r="G511" s="1"/>
@@ -9918,20 +10069,26 @@
       <c r="I511" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J511" s="1"/>
+      <c r="J511" s="1" t="s">
+        <v>894</v>
+      </c>
       <c r="K511" s="1" t="s">
-        <v>880</v>
+        <v>895</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="512" customHeight="1" ht="18.75">
-      <c r="A512" s="1"/>
+      <c r="A512" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B512" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="C512" s="1"/>
+        <v>896</v>
+      </c>
+      <c r="C512" s="1" t="s">
+        <v>897</v>
+      </c>
       <c r="D512" s="1"/>
       <c r="E512" s="1" t="s">
-        <v>882</v>
+        <v>898</v>
       </c>
       <c r="F512" s="1"/>
       <c r="G512" s="1"/>
@@ -9941,18 +10098,20 @@
       </c>
       <c r="J512" s="1"/>
       <c r="K512" s="1" t="s">
-        <v>883</v>
+        <v>899</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="513" customHeight="1" ht="18.75">
-      <c r="A513" s="1"/>
+      <c r="A513" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B513" s="1" t="s">
-        <v>884</v>
+        <v>900</v>
       </c>
       <c r="C513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1" t="s">
-        <v>885</v>
+        <v>901</v>
       </c>
       <c r="F513" s="1"/>
       <c r="G513" s="1"/>
@@ -9961,17 +10120,23 @@
         <v>420</v>
       </c>
       <c r="J513" s="1"/>
-      <c r="K513" s="1"/>
+      <c r="K513" s="1" t="s">
+        <v>902</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="514" customHeight="1" ht="18.75">
-      <c r="A514" s="1"/>
+      <c r="A514" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B514" s="1" t="s">
-        <v>886</v>
-      </c>
-      <c r="C514" s="1"/>
+        <v>903</v>
+      </c>
+      <c r="C514" s="1" t="s">
+        <v>904</v>
+      </c>
       <c r="D514" s="1"/>
       <c r="E514" s="1" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="F514" s="1"/>
       <c r="G514" s="1"/>
@@ -9980,17 +10145,21 @@
         <v>420</v>
       </c>
       <c r="J514" s="1"/>
-      <c r="K514" s="1"/>
+      <c r="K514" s="1" t="s">
+        <v>906</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="515" customHeight="1" ht="18.75">
-      <c r="A515" s="1"/>
+      <c r="A515" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B515" s="1" t="s">
-        <v>888</v>
+        <v>907</v>
       </c>
       <c r="C515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1" t="s">
-        <v>889</v>
+        <v>908</v>
       </c>
       <c r="F515" s="1"/>
       <c r="G515" s="1"/>
@@ -10000,18 +10169,20 @@
       </c>
       <c r="J515" s="1"/>
       <c r="K515" s="1" t="s">
-        <v>890</v>
+        <v>909</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="516" customHeight="1" ht="18.75">
-      <c r="A516" s="1"/>
+      <c r="A516" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B516" s="1" t="s">
-        <v>891</v>
+        <v>910</v>
       </c>
       <c r="C516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1" t="s">
-        <v>892</v>
+        <v>911</v>
       </c>
       <c r="F516" s="1"/>
       <c r="G516" s="1"/>
@@ -10021,18 +10192,22 @@
       </c>
       <c r="J516" s="1"/>
       <c r="K516" s="1" t="s">
-        <v>893</v>
+        <v>912</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="517" customHeight="1" ht="18.75">
-      <c r="A517" s="1"/>
+      <c r="A517" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B517" s="1" t="s">
-        <v>894</v>
-      </c>
-      <c r="C517" s="1"/>
+        <v>913</v>
+      </c>
+      <c r="C517" s="1" t="s">
+        <v>914</v>
+      </c>
       <c r="D517" s="1"/>
       <c r="E517" s="1" t="s">
-        <v>887</v>
+        <v>905</v>
       </c>
       <c r="F517" s="1"/>
       <c r="G517" s="1"/>
@@ -10040,18 +10215,26 @@
       <c r="I517" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J517" s="1"/>
-      <c r="K517" s="1"/>
+      <c r="J517" s="1" t="s">
+        <v>915</v>
+      </c>
+      <c r="K517" s="1" t="s">
+        <v>916</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="518" customHeight="1" ht="18.75">
-      <c r="A518" s="1"/>
+      <c r="A518" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B518" s="1" t="s">
-        <v>895</v>
-      </c>
-      <c r="C518" s="1"/>
+        <v>917</v>
+      </c>
+      <c r="C518" s="1" t="s">
+        <v>918</v>
+      </c>
       <c r="D518" s="1"/>
       <c r="E518" s="1" t="s">
-        <v>896</v>
+        <v>919</v>
       </c>
       <c r="F518" s="1"/>
       <c r="G518" s="1"/>
@@ -10060,21 +10243,23 @@
         <v>420</v>
       </c>
       <c r="J518" s="1" t="s">
-        <v>897</v>
+        <v>918</v>
       </c>
       <c r="K518" s="1" t="s">
-        <v>898</v>
+        <v>920</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="519" customHeight="1" ht="18.75">
-      <c r="A519" s="1"/>
+      <c r="A519" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B519" s="1" t="s">
-        <v>899</v>
+        <v>921</v>
       </c>
       <c r="C519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1" t="s">
-        <v>900</v>
+        <v>922</v>
       </c>
       <c r="F519" s="1"/>
       <c r="G519" s="1"/>
@@ -10082,20 +10267,24 @@
       <c r="I519" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J519" s="1"/>
+      <c r="J519" s="1" t="s">
+        <v>923</v>
+      </c>
       <c r="K519" s="1" t="s">
-        <v>901</v>
+        <v>924</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="520" customHeight="1" ht="18.75">
-      <c r="A520" s="1"/>
+      <c r="A520" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B520" s="1" t="s">
-        <v>902</v>
+        <v>925</v>
       </c>
       <c r="C520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1" t="s">
-        <v>903</v>
+        <v>926</v>
       </c>
       <c r="F520" s="1"/>
       <c r="G520" s="1"/>
@@ -10103,18 +10292,24 @@
       <c r="I520" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J520" s="1"/>
-      <c r="K520" s="1"/>
+      <c r="J520" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="K520" s="1" t="s">
+        <v>928</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="521" customHeight="1" ht="18.75">
-      <c r="A521" s="1"/>
+      <c r="A521" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B521" s="1" t="s">
-        <v>904</v>
+        <v>929</v>
       </c>
       <c r="C521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1" t="s">
-        <v>905</v>
+        <v>930</v>
       </c>
       <c r="F521" s="1"/>
       <c r="G521" s="1"/>
@@ -10123,23 +10318,25 @@
         <v>420</v>
       </c>
       <c r="J521" s="1" t="s">
-        <v>906</v>
+        <v>931</v>
       </c>
       <c r="K521" s="1" t="s">
-        <v>907</v>
+        <v>932</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="522" customHeight="1" ht="18.75">
-      <c r="A522" s="1"/>
+      <c r="A522" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B522" s="1" t="s">
-        <v>908</v>
+        <v>933</v>
       </c>
       <c r="C522" s="1"/>
       <c r="D522" s="1" t="s">
-        <v>909</v>
+        <v>934</v>
       </c>
       <c r="E522" s="1" t="s">
-        <v>910</v>
+        <v>935</v>
       </c>
       <c r="F522" s="1"/>
       <c r="G522" s="1"/>
@@ -10149,18 +10346,20 @@
       </c>
       <c r="J522" s="1"/>
       <c r="K522" s="1" t="s">
-        <v>911</v>
+        <v>936</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="523" customHeight="1" ht="18.75">
-      <c r="A523" s="1"/>
+      <c r="A523" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B523" s="1" t="s">
-        <v>912</v>
+        <v>937</v>
       </c>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1" t="s">
-        <v>913</v>
+        <v>938</v>
       </c>
       <c r="F523" s="1"/>
       <c r="G523" s="1"/>
@@ -10168,18 +10367,24 @@
       <c r="I523" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J523" s="1"/>
-      <c r="K523" s="1"/>
+      <c r="J523" s="1" t="s">
+        <v>939</v>
+      </c>
+      <c r="K523" s="1" t="s">
+        <v>940</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="524" customHeight="1" ht="18.75">
-      <c r="A524" s="1"/>
+      <c r="A524" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B524" s="1" t="s">
-        <v>914</v>
+        <v>941</v>
       </c>
       <c r="C524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1" t="s">
-        <v>915</v>
+        <v>942</v>
       </c>
       <c r="F524" s="1"/>
       <c r="G524" s="1"/>
@@ -10188,19 +10393,23 @@
         <v>420</v>
       </c>
       <c r="J524" s="1"/>
-      <c r="K524" s="1"/>
+      <c r="K524" s="1" t="s">
+        <v>943</v>
+      </c>
     </row>
     <row x14ac:dyDescent="0.25" r="525" customHeight="1" ht="18.75">
-      <c r="A525" s="1"/>
+      <c r="A525" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B525" s="1" t="s">
-        <v>916</v>
+        <v>944</v>
       </c>
       <c r="C525" s="1"/>
       <c r="D525" s="1" t="s">
-        <v>875</v>
+        <v>888</v>
       </c>
       <c r="E525" s="1" t="s">
-        <v>917</v>
+        <v>945</v>
       </c>
       <c r="F525" s="1"/>
       <c r="G525" s="1"/>
@@ -10209,23 +10418,25 @@
         <v>420</v>
       </c>
       <c r="J525" s="1" t="s">
-        <v>918</v>
+        <v>946</v>
       </c>
       <c r="K525" s="1" t="s">
-        <v>919</v>
+        <v>947</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="526" customHeight="1" ht="18.75">
-      <c r="A526" s="1"/>
+      <c r="A526" s="1" t="s">
+        <v>855</v>
+      </c>
       <c r="B526" s="1" t="s">
-        <v>920</v>
+        <v>948</v>
       </c>
       <c r="C526" s="1"/>
       <c r="D526" s="1" t="s">
-        <v>921</v>
+        <v>949</v>
       </c>
       <c r="E526" s="1" t="s">
-        <v>922</v>
+        <v>950</v>
       </c>
       <c r="F526" s="1"/>
       <c r="G526" s="1"/>
@@ -10235,18 +10446,22 @@
       </c>
       <c r="J526" s="1"/>
       <c r="K526" s="1" t="s">
-        <v>923</v>
+        <v>951</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="527" customHeight="1" ht="18.75">
-      <c r="A527" s="1"/>
+      <c r="A527" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B527" s="1" t="s">
-        <v>924</v>
-      </c>
-      <c r="C527" s="1"/>
+        <v>952</v>
+      </c>
+      <c r="C527" s="1" t="s">
+        <v>953</v>
+      </c>
       <c r="D527" s="1"/>
       <c r="E527" s="1" t="s">
-        <v>925</v>
+        <v>954</v>
       </c>
       <c r="F527" s="1"/>
       <c r="G527" s="1"/>
@@ -10254,20 +10469,26 @@
       <c r="I527" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J527" s="1"/>
+      <c r="J527" s="1" t="s">
+        <v>955</v>
+      </c>
       <c r="K527" s="1" t="s">
-        <v>926</v>
+        <v>956</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="528" customHeight="1" ht="18.75">
-      <c r="A528" s="1"/>
+      <c r="A528" s="1" t="s">
+        <v>865</v>
+      </c>
       <c r="B528" s="1" t="s">
-        <v>927</v>
-      </c>
-      <c r="C528" s="1"/>
+        <v>957</v>
+      </c>
+      <c r="C528" s="1" t="s">
+        <v>958</v>
+      </c>
       <c r="D528" s="1"/>
       <c r="E528" s="1" t="s">
-        <v>928</v>
+        <v>959</v>
       </c>
       <c r="F528" s="1"/>
       <c r="G528" s="1"/>
@@ -10275,9 +10496,11 @@
       <c r="I528" s="1" t="s">
         <v>420</v>
       </c>
-      <c r="J528" s="1"/>
+      <c r="J528" s="1" t="s">
+        <v>960</v>
+      </c>
       <c r="K528" s="1" t="s">
-        <v>929</v>
+        <v>961</v>
       </c>
     </row>
     <row x14ac:dyDescent="0.25" r="529" customHeight="1" ht="18.75">
@@ -16706,7 +16929,7 @@
       <c r="G14" s="1"/>
       <c r="H14" s="1"/>
     </row>
-    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="22.5">
+    <row x14ac:dyDescent="0.25" r="15" customHeight="1" ht="18.75">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
